--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -24706,6 +24706,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1059">
+      <c r="A1059" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1059" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="G1059" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1060" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1060" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="G1060" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -24752,6 +24752,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1061">
+      <c r="A1061" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1061" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1061" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="G1061" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -24775,6 +24775,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1062">
+      <c r="A1062" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1062" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1062" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="G1062" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -24616,7 +24616,7 @@
     </row>
     <row r="1055">
       <c r="A1055" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1055" t="n">
         <v>0</v>
@@ -24639,22 +24639,22 @@
     </row>
     <row r="1056">
       <c r="A1056" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1056" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="C1056" t="n">
-        <v>0.689999997615814</v>
+        <v>0.714999973773956</v>
       </c>
       <c r="D1056" t="n">
-        <v>0.689999997615814</v>
+        <v>0.714999973773956</v>
       </c>
       <c r="E1056" t="n">
-        <v>0.689999997615814</v>
+        <v>0.714999973773956</v>
       </c>
       <c r="F1056" t="n">
-        <v>0.689999997615814</v>
+        <v>0.714999973773956</v>
       </c>
       <c r="G1056" t="s">
         <v>7</v>
@@ -24662,10 +24662,10 @@
     </row>
     <row r="1057">
       <c r="A1057" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1057" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="C1057" t="n">
         <v>0.689999997615814</v>
@@ -24685,22 +24685,22 @@
     </row>
     <row r="1058">
       <c r="A1058" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1058" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C1058" t="n">
-        <v>0.720000028610229</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="D1058" t="n">
-        <v>0.720000028610229</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="E1058" t="n">
-        <v>0.720000028610229</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="F1058" t="n">
-        <v>0.720000028610229</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="G1058" t="s">
         <v>7</v>
@@ -24708,10 +24708,10 @@
     </row>
     <row r="1059">
       <c r="A1059" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1059" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C1059" t="n">
         <v>0.720000028610229</v>
@@ -24731,22 +24731,22 @@
     </row>
     <row r="1060">
       <c r="A1060" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1060" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C1060" t="n">
-        <v>0.689999997615814</v>
+        <v>0.720000028610229</v>
       </c>
       <c r="D1060" t="n">
-        <v>0.689999997615814</v>
+        <v>0.720000028610229</v>
       </c>
       <c r="E1060" t="n">
-        <v>0.689999997615814</v>
+        <v>0.720000028610229</v>
       </c>
       <c r="F1060" t="n">
-        <v>0.689999997615814</v>
+        <v>0.720000028610229</v>
       </c>
       <c r="G1060" t="s">
         <v>7</v>
@@ -24754,22 +24754,22 @@
     </row>
     <row r="1061">
       <c r="A1061" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1061" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="C1061" t="n">
-        <v>0.699999988079071</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="D1061" t="n">
-        <v>0.699999988079071</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="E1061" t="n">
-        <v>0.699999988079071</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="F1061" t="n">
-        <v>0.699999988079071</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="G1061" t="s">
         <v>7</v>
@@ -24777,22 +24777,22 @@
     </row>
     <row r="1062">
       <c r="A1062" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1062" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="C1062" t="n">
-        <v>0.689999997615814</v>
+        <v>0.699999988079071</v>
       </c>
       <c r="D1062" t="n">
-        <v>0.689999997615814</v>
+        <v>0.699999988079071</v>
       </c>
       <c r="E1062" t="n">
-        <v>0.689999997615814</v>
+        <v>0.699999988079071</v>
       </c>
       <c r="F1062" t="n">
-        <v>0.689999997615814</v>
+        <v>0.699999988079071</v>
       </c>
       <c r="G1062" t="s">
         <v>7</v>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -24867,6 +24867,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1066">
+      <c r="A1066" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1066" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="G1066" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -24890,6 +24890,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="G1067" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -24913,6 +24913,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="G1068" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -24936,6 +24936,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1069">
+      <c r="A1069" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1069" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="G1069" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -28221,6 +28221,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1072" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="H1072" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -25044,7 +25044,9 @@
       <c r="E1073" t="n">
         <v>0.660000026226044</v>
       </c>
-      <c r="F1073"/>
+      <c r="F1073" t="n">
+        <v>0.654999971389771</v>
+      </c>
       <c r="G1073" t="s">
         <v>7</v>
       </c>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -25051,6 +25051,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1074">
+      <c r="A1074" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1074" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="G1074" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -25074,6 +25074,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1075">
+      <c r="A1075" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1075" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="G1075" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1076" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="F1076"/>
+      <c r="G1076" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -25108,13 +25108,36 @@
         <v>0.615000009536743</v>
       </c>
       <c r="D1076" t="n">
-        <v>0.584999978542328</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="E1076" t="n">
         <v>0.615000009536743</v>
       </c>
-      <c r="F1076"/>
+      <c r="F1076" t="n">
+        <v>0.574999988079071</v>
+      </c>
       <c r="G1076" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1077" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1077"/>
+      <c r="G1077" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -25136,8 +25136,31 @@
       <c r="E1077" t="n">
         <v>0.550000011920929</v>
       </c>
-      <c r="F1077"/>
+      <c r="F1077" t="n">
+        <v>0.550000011920929</v>
+      </c>
       <c r="G1077" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1078" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1078" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F1078"/>
+      <c r="G1078" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -25159,8 +25159,31 @@
       <c r="E1078" t="n">
         <v>0.545000016689301</v>
       </c>
-      <c r="F1078"/>
+      <c r="F1078" t="n">
+        <v>0.545000016689301</v>
+      </c>
       <c r="G1078" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1079" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="F1079"/>
+      <c r="G1079" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -25189,6 +25189,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1080" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="G1080" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -28507,6 +28507,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1083">
+      <c r="A1083" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1083" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="H1083" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -28533,6 +28533,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1084" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="H1084" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -31814,6 +31814,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1085">
+      <c r="A1085" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1085" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I1085" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1086" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="H1086" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I1086" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -31872,6 +31872,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1087">
+      <c r="A1087" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1087" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>0.488000005483627</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>0.488000005483627</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1087" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -31901,6 +31901,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1088">
+      <c r="A1088" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1088" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>0.486000001430511</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>0.488000005483627</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I1088" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -31930,6 +31930,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1089">
+      <c r="A1089" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1089" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>0.44200000166893</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I1089" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -31959,6 +31959,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1090">
+      <c r="A1090" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1090" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>0.488000005483627</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>54000</v>
+      </c>
+      <c r="I1090" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -31988,6 +31988,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1091">
+      <c r="A1091" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1091" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>0.474000006914139</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I1091" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -32017,6 +32017,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1092">
+      <c r="A1092" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1092" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I1092" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -32046,6 +32046,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1093">
+      <c r="A1093" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1093" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>0.486000001430511</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>58000</v>
+      </c>
+      <c r="I1093" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GML.MI.xlsx
+++ b/data/GML.MI.xlsx
@@ -32060,7 +32060,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="E1093" t="n">
-        <v>0.486000001430511</v>
+        <v>0.493999987840652</v>
       </c>
       <c r="F1093" t="n">
         <v>0.514999985694885</v>
@@ -32072,6 +32072,35 @@
         <v>58000</v>
       </c>
       <c r="I1093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1094" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1094" t="s">
         <v>9</v>
       </c>
     </row>
